--- a/output/pdf_financials_xlsx/AEM.xlsx
+++ b/output/pdf_financials_xlsx/AEM.xlsx
@@ -2977,34 +2977,34 @@
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>9471.433999999999</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>8878.584000000001</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>10033.352</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>11255.516</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>12071.818</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>26077.86</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0</v>
+        <v>32470.421</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0</v>
+        <v>34324.889</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>0</v>
+        <v>37100.157</v>
       </c>
     </row>
     <row r="57">
@@ -3318,31 +3318,31 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>92.27500000000001</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>121.633</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>111.173</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>144.135</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>163.032</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>158.317</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>189.069</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>259.002</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>317.888</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -3447,37 +3447,37 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>37.886</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>51.533</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>55.893</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>76.562</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>75.28700000000001</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>102.957</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>104.551</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>250.894</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>253.806</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>276.462</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>283.883</v>
       </c>
     </row>
     <row r="68">
@@ -3588,25 +3588,25 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>1.914</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>14.693</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>32.988</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>36.466</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>46.394</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>40.305</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="71">
@@ -3631,25 +3631,25 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>1.914</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>360</v>
+        <v>374.693</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>225</v>
+        <v>257.988</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>100</v>
+        <v>136.466</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>100</v>
+        <v>146.394</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>90</v>
+        <v>130.305</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="72">
@@ -3803,25 +3803,25 @@
         <v>43.099</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>50.852</v>
+        <v>48.938</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>70.066</v>
+        <v>55.373</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>122.14</v>
+        <v>89.152</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>173.919</v>
+        <v>137.453</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>197.646</v>
+        <v>151.252</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>598.553</v>
+        <v>558.248</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>1438.762</v>
+        <v>1408.282</v>
       </c>
     </row>
     <row r="76">
@@ -3935,22 +3935,22 @@
         <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0</v>
+        <v>102.135</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>98.44499999999999</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>114.876</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>115.154</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>98.92100000000001</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>94.71899999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3978,22 +3978,22 @@
         <v>1721.308</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1364.108</v>
+        <v>1466.243</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1340.223</v>
+        <v>1438.668</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>1242.07</v>
+        <v>1356.946</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>1743.086</v>
+        <v>1858.24</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1052.956</v>
+        <v>1151.877</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>196.271</v>
+        <v>290.99</v>
       </c>
     </row>
     <row r="80">
@@ -4018,25 +4018,25 @@
         <v>0.2773101871420425</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.3783084528128717</v>
+        <v>0.3787291110441027</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.3372988903092117</v>
+        <v>0.3601547408458629</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.2608804569374398</v>
+        <v>0.2827867930292673</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.08263293464919315</v>
+        <v>0.09195125157430004</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.09489234751838228</v>
+        <v>0.1032097396297106</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.05486302915100634</v>
+        <v>0.06154601615713607</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.007932556757483814</v>
+        <v>0.01299264293160132</v>
       </c>
     </row>
     <row r="81">
@@ -4236,22 +4236,22 @@
         <v>1220.074</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>1538.625</v>
+        <v>1436.49</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>2114.283</v>
+        <v>2015.838</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>5064.971</v>
+        <v>4950.095</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>6470.922</v>
+        <v>6355.768</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>6589.197</v>
+        <v>6490.276</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>7060.35</v>
+        <v>6965.631</v>
       </c>
     </row>
     <row r="86">
@@ -5755,19 +5755,19 @@
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-34.606</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-109.955</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-47.003</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-169.357</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-682.89</v>
       </c>
     </row>
     <row r="122">
@@ -7698,7 +7698,11 @@
           <t>Lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -8016,7 +8020,11 @@
           <t>Lease obligations (Note 13)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -19462,7 +19470,11 @@
           <t>Repurchase of common shares (Notes 16 and 17)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -21940,7 +21952,11 @@
           <t>Repurchase of common shares (Notes 16 and 17C,D)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
